--- a/appointment_forms/018_open_day_appointment_scheduling--appointment_forms.xlsx
+++ b/appointment_forms/018_open_day_appointment_scheduling--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_page_1</t>
+          <t>campus_visit_time_slots</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_page_2</t>
+          <t>visitor_information</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_page_3</t>
+          <t>booking_information</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_page_4</t>
+          <t>campus_visit_booking_information</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_page_5</t>
+          <t>booking_status</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,41 +635,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_page_6</t>
+          <t>booking_status_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Booking Status</t>
+          <t>Is the booking active?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_page_7</t>
+          <t>visitor_information_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Booking Status</t>
+          <t>Visitor Contact Information</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,41 +681,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_page_8</t>
+          <t>booking_status_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Booking Status</t>
+          <t>Booking Status 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_page_9</t>
+          <t>booking_confirmation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Visitor Information</t>
+          <t>Is the booking confirmed?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_page_10</t>
+          <t>booking_status_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Booking Status</t>
+          <t>Booking Status 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_page_11</t>
+          <t>booking_status_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Booking Status</t>
+          <t>Booking Status 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_page_12</t>
+          <t>booking_status_6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Booking Status</t>
+          <t>Booking Status 6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,304 +827,321 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_page_1_choices</t>
+          <t>campus_visit_time_slots_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_page_1_choices</t>
+          <t>campus_visit_time_slots_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_page_3_choices</t>
+          <t>campus_visit_time_slots_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_page_3_choices</t>
+          <t>booking_information_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_page_6_choices</t>
+          <t>booking_information_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_page_6_choices</t>
+          <t>booking_status_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_page_7_choices</t>
+          <t>booking_status_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_page_7_choices</t>
+          <t>visitor_information_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_page_8_choices</t>
+          <t>visitor_information_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_page_8_choices</t>
+          <t>booking_status_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_page_9_choices</t>
+          <t>booking_status_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_page_9_choices</t>
+          <t>booking_confirmation_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>form_page_10_choices</t>
+          <t>booking_confirmation_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>form_page_10_choices</t>
+          <t>booking_status_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_page_11_choices</t>
+          <t>booking_status_4_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>form_page_11_choices</t>
+          <t>booking_status_5_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>form_page_12_choices</t>
+          <t>booking_status_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>form_page_12_choices</t>
+          <t>booking_status_6_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>booking_status_6_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>inactive</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
